--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11926,6 +11926,60 @@
         <v>302</v>
       </c>
       <c r="G426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>284.59</v>
+      </c>
+      <c r="C427" t="n">
+        <v>267.63</v>
+      </c>
+      <c r="D427" t="n">
+        <v>287.88</v>
+      </c>
+      <c r="E427" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="F427" t="n">
+        <v>302.97</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>284.15</v>
+      </c>
+      <c r="C428" t="n">
+        <v>266.29</v>
+      </c>
+      <c r="D428" t="n">
+        <v>288.48</v>
+      </c>
+      <c r="E428" t="n">
+        <v>289.65</v>
+      </c>
+      <c r="F428" t="n">
+        <v>302.59</v>
+      </c>
+      <c r="G428" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11942,7 +11996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B475"/>
+  <dimension ref="A1:B477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16695,6 +16749,26 @@
       </c>
       <c r="B475" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -16863,28 +16937,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2868509764829495</v>
+        <v>-0.3005925851624535</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02001462256050024</v>
+        <v>0.02203572155709299</v>
       </c>
       <c r="M2" t="n">
-        <v>12.58770753984065</v>
+        <v>12.60010651842667</v>
       </c>
       <c r="N2" t="n">
-        <v>213.9822138629726</v>
+        <v>214.0148365975508</v>
       </c>
       <c r="O2" t="n">
-        <v>14.62813090804743</v>
+        <v>14.62924593400326</v>
       </c>
       <c r="P2" t="n">
-        <v>307.04938623308</v>
+        <v>307.2058329714262</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16945,28 +17019,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5714692114593234</v>
+        <v>-0.5921594091070631</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K3" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06219637346168982</v>
+        <v>0.06650626475100496</v>
       </c>
       <c r="M3" t="n">
-        <v>13.40125441890557</v>
+        <v>13.44653648960551</v>
       </c>
       <c r="N3" t="n">
-        <v>262.4629294166427</v>
+        <v>263.6172256618618</v>
       </c>
       <c r="O3" t="n">
-        <v>16.20070768258729</v>
+        <v>16.23629347055115</v>
       </c>
       <c r="P3" t="n">
-        <v>305.0236343800757</v>
+        <v>305.2581828702022</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17027,28 +17101,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7560112245777451</v>
+        <v>-0.771669365553871</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4418195489494136</v>
+        <v>0.4456642411062399</v>
       </c>
       <c r="M4" t="n">
-        <v>5.00099781221728</v>
+        <v>5.070312761450483</v>
       </c>
       <c r="N4" t="n">
-        <v>38.44899700247201</v>
+        <v>39.63220478779237</v>
       </c>
       <c r="O4" t="n">
-        <v>6.200725522265278</v>
+        <v>6.295411407349989</v>
       </c>
       <c r="P4" t="n">
-        <v>325.6843507194296</v>
+        <v>325.8618264760175</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17105,28 +17179,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5914161675337255</v>
+        <v>-0.6049771469464184</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3590453573390532</v>
+        <v>0.3647016551383666</v>
       </c>
       <c r="M5" t="n">
-        <v>4.795388323418712</v>
+        <v>4.862954837641603</v>
       </c>
       <c r="N5" t="n">
-        <v>33.2478220272971</v>
+        <v>34.11446279358212</v>
       </c>
       <c r="O5" t="n">
-        <v>5.766092440058267</v>
+        <v>5.840758751530671</v>
       </c>
       <c r="P5" t="n">
-        <v>320.6348805512154</v>
+        <v>320.7885885299873</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17183,28 +17257,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4472366990281428</v>
+        <v>-0.4588124606651283</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2278732392499205</v>
+        <v>0.2350163674310434</v>
       </c>
       <c r="M6" t="n">
-        <v>4.762343844582756</v>
+        <v>4.809916418155753</v>
       </c>
       <c r="N6" t="n">
-        <v>36.08851229224359</v>
+        <v>36.66443953125934</v>
       </c>
       <c r="O6" t="n">
-        <v>6.007371496107393</v>
+        <v>6.055116805748617</v>
       </c>
       <c r="P6" t="n">
-        <v>327.50510081099</v>
+        <v>327.6363072308731</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17242,7 +17316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32983,6 +33057,80 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-45.1218717078075,170.98041729741354</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-45.12209884508874,170.97947522231016</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-45.12270400726389,170.97889076129974</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-45.123180393705496,170.97825140116134</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-45.12373090729518,170.97774869834652</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-45.121868288228576,170.98041447794714</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-45.1220890258923,170.9794653355678</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-45.12270800167338,170.9788958927849</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-45.123177721313276,170.9782476259052</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-45.12372853542957,170.977745218833</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G428"/>
+  <dimension ref="A1:G431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11980,6 +11980,87 @@
         <v>302.59</v>
       </c>
       <c r="G428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:13:47+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>283.52</v>
+      </c>
+      <c r="C429" t="n">
+        <v>264.73</v>
+      </c>
+      <c r="D429" t="n">
+        <v>288.89</v>
+      </c>
+      <c r="E429" t="n">
+        <v>289.79</v>
+      </c>
+      <c r="F429" t="n">
+        <v>302.29</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="C430" t="n">
+        <v>265.48</v>
+      </c>
+      <c r="D430" t="n">
+        <v>289.34</v>
+      </c>
+      <c r="E430" t="n">
+        <v>290.03</v>
+      </c>
+      <c r="F430" t="n">
+        <v>301.92</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>283.62</v>
+      </c>
+      <c r="C431" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="D431" t="n">
+        <v>289.94</v>
+      </c>
+      <c r="E431" t="n">
+        <v>290.61</v>
+      </c>
+      <c r="F431" t="n">
+        <v>301.99</v>
+      </c>
+      <c r="G431" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11996,7 +12077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B477"/>
+  <dimension ref="A1:B480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16769,6 +16850,36 @@
       </c>
       <c r="B477" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -16937,28 +17048,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3005925851624535</v>
+        <v>-0.3216921174664632</v>
       </c>
       <c r="J2" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K2" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02203572155709299</v>
+        <v>0.0253138791293549</v>
       </c>
       <c r="M2" t="n">
-        <v>12.60010651842667</v>
+        <v>12.62037376230317</v>
       </c>
       <c r="N2" t="n">
-        <v>214.0148365975508</v>
+        <v>214.1766217686475</v>
       </c>
       <c r="O2" t="n">
-        <v>14.62924593400326</v>
+        <v>14.63477440101649</v>
       </c>
       <c r="P2" t="n">
-        <v>307.2058329714262</v>
+        <v>307.4466960343715</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17019,28 +17130,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5921594091070631</v>
+        <v>-0.6238948195288672</v>
       </c>
       <c r="J3" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K3" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06650626475100496</v>
+        <v>0.07327158367780884</v>
       </c>
       <c r="M3" t="n">
-        <v>13.44653648960551</v>
+        <v>13.51705291529813</v>
       </c>
       <c r="N3" t="n">
-        <v>263.6172256618618</v>
+        <v>265.5834755319609</v>
       </c>
       <c r="O3" t="n">
-        <v>16.23629347055115</v>
+        <v>16.29673205068921</v>
       </c>
       <c r="P3" t="n">
-        <v>305.2581828702022</v>
+        <v>305.6188892484975</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17101,28 +17212,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.771669365553871</v>
+        <v>-0.7927765618777087</v>
       </c>
       <c r="J4" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K4" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4456642411062399</v>
+        <v>0.4521871859096994</v>
       </c>
       <c r="M4" t="n">
-        <v>5.070312761450483</v>
+        <v>5.165448971150668</v>
       </c>
       <c r="N4" t="n">
-        <v>39.63220478779237</v>
+        <v>41.03590725263069</v>
       </c>
       <c r="O4" t="n">
-        <v>6.295411407349989</v>
+        <v>6.405927509161393</v>
       </c>
       <c r="P4" t="n">
-        <v>325.8618264760175</v>
+        <v>326.1017005278648</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17179,28 +17290,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6049771469464184</v>
+        <v>-0.6242913099373172</v>
       </c>
       <c r="J5" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3647016551383666</v>
+        <v>0.3731701921792109</v>
       </c>
       <c r="M5" t="n">
-        <v>4.862954837641603</v>
+        <v>4.958048572498893</v>
       </c>
       <c r="N5" t="n">
-        <v>34.11446279358212</v>
+        <v>35.28302184631583</v>
       </c>
       <c r="O5" t="n">
-        <v>5.840758751530671</v>
+        <v>5.939951333665607</v>
       </c>
       <c r="P5" t="n">
-        <v>320.7885885299873</v>
+        <v>321.0080864423226</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17257,28 +17368,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4588124606651283</v>
+        <v>-0.4765930997664093</v>
       </c>
       <c r="J6" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2350163674310434</v>
+        <v>0.2456130026775308</v>
       </c>
       <c r="M6" t="n">
-        <v>4.809916418155753</v>
+        <v>4.885862749260244</v>
       </c>
       <c r="N6" t="n">
-        <v>36.66443953125934</v>
+        <v>37.5999130232392</v>
       </c>
       <c r="O6" t="n">
-        <v>6.055116805748617</v>
+        <v>6.131876794525409</v>
       </c>
       <c r="P6" t="n">
-        <v>327.6363072308731</v>
+        <v>327.8383849222355</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17316,7 +17427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G428"/>
+  <dimension ref="A1:G431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33131,6 +33242,117 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:13:47+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-45.12186339201322,170.98041044098446</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-45.12207759458798,170.9794538256332</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-45.122710731186416,170.97889939930016</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-45.12317861211069,170.97824888432385</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-45.12372666290402,170.9777424718489</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-45.121863236577795,170.98041031282693</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-45.122083090407514,170.97945935925506</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-45.12271372699329,170.97890324791487</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-45.12318013919196,170.97825104161313</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-45.123724353455735,170.9777390839021</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-45.12186416919027,170.98041108177213</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-45.12209415532338,170.97947050028353</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-45.122717721402246,170.97890837940173</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-45.12318382963818,170.97825625506266</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-45.1237247903784,170.97773972486496</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0473/nzd0473.xlsx
+++ b/data/nzd0473/nzd0473.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G431"/>
+  <dimension ref="A1:G433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12061,6 +12061,60 @@
         <v>301.99</v>
       </c>
       <c r="G431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:14:04+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>282.04</v>
+      </c>
+      <c r="C432" t="n">
+        <v>265.7</v>
+      </c>
+      <c r="D432" t="n">
+        <v>289.64</v>
+      </c>
+      <c r="E432" t="n">
+        <v>291.32</v>
+      </c>
+      <c r="F432" t="n">
+        <v>303.05</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>280.56</v>
+      </c>
+      <c r="C433" t="n">
+        <v>264.17</v>
+      </c>
+      <c r="D433" t="n">
+        <v>289.65</v>
+      </c>
+      <c r="E433" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="F433" t="n">
+        <v>304.39</v>
+      </c>
+      <c r="G433" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12077,7 +12131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B480"/>
+  <dimension ref="A1:B482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16880,6 +16934,26 @@
       </c>
       <c r="B480" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -17048,28 +17122,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3216921174664632</v>
+        <v>-0.3374094439952429</v>
       </c>
       <c r="J2" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0253138791293549</v>
+        <v>0.027855271008838</v>
       </c>
       <c r="M2" t="n">
-        <v>12.62037376230317</v>
+        <v>12.64137024134863</v>
       </c>
       <c r="N2" t="n">
-        <v>214.1766217686475</v>
+        <v>214.58041143492</v>
       </c>
       <c r="O2" t="n">
-        <v>14.63477440101649</v>
+        <v>14.64856345977038</v>
       </c>
       <c r="P2" t="n">
-        <v>307.4466960343715</v>
+        <v>307.6270092379839</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17130,28 +17204,28 @@
         <v>0.079</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6238948195288672</v>
+        <v>-0.6451922552267858</v>
       </c>
       <c r="J3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07327158367780884</v>
+        <v>0.07793933803061515</v>
       </c>
       <c r="M3" t="n">
-        <v>13.51705291529813</v>
+        <v>13.56283734923094</v>
       </c>
       <c r="N3" t="n">
-        <v>265.5834755319609</v>
+        <v>266.9455277786575</v>
       </c>
       <c r="O3" t="n">
-        <v>16.29673205068921</v>
+        <v>16.33846773044086</v>
       </c>
       <c r="P3" t="n">
-        <v>305.6188892484975</v>
+        <v>305.8621643905244</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17212,28 +17286,28 @@
         <v>0.056</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7927765618777087</v>
+        <v>-0.8062026085927836</v>
       </c>
       <c r="J4" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K4" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4521871859096994</v>
+        <v>0.4566953746960527</v>
       </c>
       <c r="M4" t="n">
-        <v>5.165448971150668</v>
+        <v>5.223623210479624</v>
       </c>
       <c r="N4" t="n">
-        <v>41.03590725263069</v>
+        <v>41.87387974118079</v>
       </c>
       <c r="O4" t="n">
-        <v>6.405927509161393</v>
+        <v>6.471002993445513</v>
       </c>
       <c r="P4" t="n">
-        <v>326.1017005278648</v>
+        <v>326.2550355923416</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17290,28 +17364,28 @@
         <v>0.0696</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6242913099373172</v>
+        <v>-0.6352456021153193</v>
       </c>
       <c r="J5" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K5" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3731701921792109</v>
+        <v>0.379013106535649</v>
       </c>
       <c r="M5" t="n">
-        <v>4.958048572498893</v>
+        <v>5.008549691652188</v>
       </c>
       <c r="N5" t="n">
-        <v>35.28302184631583</v>
+        <v>35.80548443782345</v>
       </c>
       <c r="O5" t="n">
-        <v>5.939951333665607</v>
+        <v>5.983768414454511</v>
       </c>
       <c r="P5" t="n">
-        <v>321.0080864423226</v>
+        <v>321.1331896382194</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17368,28 +17442,28 @@
         <v>0.0713</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4765930997664093</v>
+        <v>-0.4866302236526244</v>
       </c>
       <c r="J6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2456130026775308</v>
+        <v>0.2523146357712969</v>
       </c>
       <c r="M6" t="n">
-        <v>4.885862749260244</v>
+        <v>4.926541108398424</v>
       </c>
       <c r="N6" t="n">
-        <v>37.5999130232392</v>
+        <v>38.00253853193988</v>
       </c>
       <c r="O6" t="n">
-        <v>6.131876794525409</v>
+        <v>6.164619901659784</v>
       </c>
       <c r="P6" t="n">
-        <v>327.8383849222355</v>
+        <v>327.9530128258254</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17427,7 +17501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G431"/>
+  <dimension ref="A1:G433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33353,6 +33427,80 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:14:04+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-45.12185188979242,170.9804009573288</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-45.12208470251452,170.97946098245097</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-45.12271572419779,170.97890581365823</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-45.12318834725307,170.9782626370449</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-45.123731406635294,170.9777494308757</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-45.12184038757091,170.98039147367692</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-45.122073491042556,170.97944969386293</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-45.122715790771274,170.978905899183</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-45.123195346374054,170.978272524625</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-45.12373977058157,170.9777617007415</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
